--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.MOHAMMED13\Desktop\StudentSearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC96171-76E8-46E5-90CA-2E323B1BF2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73B42CF-44A3-474D-AAC3-2FF6BB084277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="7270" xr2:uid="{09B08D6D-2074-4FE1-91E8-DA8DA0A4DB1F}"/>
   </bookViews>
